--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B5737F-CDF7-416F-A6F9-2DB88176B3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2807E1-9721-4A00-9178-081719746D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -81,10 +81,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>attackCooldawn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>range</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -106,6 +102,10 @@
   </si>
   <si>
     <t>Boom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attackCooldown</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -516,21 +516,21 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2807E1-9721-4A00-9178-081719746D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A7E193-86C2-4A36-B49F-D6C3A0849DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +106,10 @@
   </si>
   <si>
     <t>attackCooldown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knockbackPower</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -498,11 +502,12 @@
     <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="16.3125" customWidth="1"/>
     <col min="5" max="5" width="17.75" customWidth="1"/>
-    <col min="7" max="7" width="28.8125" customWidth="1"/>
-    <col min="8" max="8" width="43.3125" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="23.875" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -522,13 +527,16 @@
         <v>10</v>
       </c>
       <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -547,8 +555,11 @@
       <c r="F2">
         <v>2</v>
       </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -567,8 +578,11 @@
       <c r="F3">
         <v>10</v>
       </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,6 +599,9 @@
         <v>3</v>
       </c>
       <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
         <v>7</v>
       </c>
     </row>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A7E193-86C2-4A36-B49F-D6C3A0849DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE390726-B1BF-4BFB-B58B-9BD7E78AC377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,22 +49,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>야구방망이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>폭탄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Throw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>weaponId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -93,14 +81,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Gun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Boom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -110,6 +90,38 @@
   </si>
   <si>
     <t>knockbackPower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -509,77 +521,77 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.6">
@@ -587,22 +599,68 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>40</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE390726-B1BF-4BFB-B58B-9BD7E78AC377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756EEF0A-2DE3-41E7-90EE-AC69E2F28ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -97,10 +97,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Arrow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Shield</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,6 +118,23 @@
   </si>
   <si>
     <t>망치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapons/Bow</t>
+  </si>
+  <si>
+    <t>Bow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapons/Shield</t>
+  </si>
+  <si>
+    <t>Weapons/Sword</t>
+  </si>
+  <si>
+    <t>Weapons/Hammer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -129,7 +142,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +157,12 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,8 +187,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -507,7 +529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="2" width="13.0625" customWidth="1"/>
@@ -519,7 +541,7 @@
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -548,7 +570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -556,7 +578,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -570,16 +592,19 @@
       <c r="G2">
         <v>3</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>20</v>
@@ -593,16 +618,19 @@
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>20</v>
@@ -616,16 +644,19 @@
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>40</v>
@@ -639,8 +670,11 @@
       <c r="G5">
         <v>5</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>10</v>
       </c>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756EEF0A-2DE3-41E7-90EE-AC69E2F28ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A837B-61BD-4F6A-928E-032461C834AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,6 +135,10 @@
   </si>
   <si>
     <t>Weapons/Hammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attackDuration</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -528,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -536,12 +540,14 @@
     <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="16.3125" customWidth="1"/>
     <col min="5" max="5" width="17.75" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16.6875" customWidth="1"/>
+    <col min="7" max="7" width="13.3125" customWidth="1"/>
     <col min="8" max="8" width="23.875" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="9" max="9" width="23.75" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -558,19 +564,22 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -587,16 +596,19 @@
         <v>1</v>
       </c>
       <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -613,16 +625,19 @@
         <v>1.5</v>
       </c>
       <c r="F3">
+        <v>0.3</v>
+      </c>
+      <c r="G3">
         <v>10</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -636,19 +651,22 @@
         <v>20</v>
       </c>
       <c r="E4">
+        <v>0.2</v>
+      </c>
+      <c r="F4">
+        <v>0.5</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -665,16 +683,19 @@
         <v>2</v>
       </c>
       <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>5</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -691,9 +712,12 @@
         <v>3</v>
       </c>
       <c r="F6">
+        <v>0.6</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>8</v>
       </c>
     </row>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A837B-61BD-4F6A-928E-032461C834AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC5B353-2469-4B2A-8234-DDA0833C3F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="31">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -140,6 +140,23 @@
   <si>
     <t>attackDuration</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>projectileId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Emmhield</t>
+  </si>
+  <si>
+    <t>Emmammer</t>
+  </si>
+  <si>
+    <t>Arroom</t>
   </si>
 </sst>
 </file>
@@ -532,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -544,10 +561,11 @@
     <col min="7" max="7" width="13.3125" customWidth="1"/>
     <col min="8" max="8" width="23.875" customWidth="1"/>
     <col min="9" max="9" width="23.75" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="10" max="10" width="19.375" customWidth="1"/>
+    <col min="11" max="11" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -573,13 +591,16 @@
         <v>12</v>
       </c>
       <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -602,13 +623,13 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -631,13 +652,16 @@
         <v>10</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -660,13 +684,13 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -689,13 +713,13 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -718,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC5B353-2469-4B2A-8234-DDA0833C3F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA8B951-B548-4909-A7E2-334942418F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>폭탄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>weaponId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -77,14 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>iconAddressable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boom</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>attackCooldown</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,16 +135,6 @@
   </si>
   <si>
     <t>Arrow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Emmhield</t>
-  </si>
-  <si>
-    <t>Emmammer</t>
-  </si>
-  <si>
-    <t>Arroom</t>
   </si>
 </sst>
 </file>
@@ -549,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -565,50 +543,47 @@
     <col min="11" max="11" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -626,18 +601,18 @@
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>20</v>
@@ -655,21 +630,21 @@
         <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>20</v>
@@ -687,18 +662,18 @@
         <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>40</v>
@@ -707,7 +682,7 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -716,33 +691,7 @@
         <v>12</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>40</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>0.6</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA8B951-B548-4909-A7E2-334942418F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD724CF-C41F-4F72-A078-4DA3B92E024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,6 +135,26 @@
   </si>
   <si>
     <t>Arrow</t>
+  </si>
+  <si>
+    <t>soundAddressable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sounds/Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sounds/Bow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sounds/Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sounds/Hammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -527,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -543,7 +563,7 @@
     <col min="11" max="11" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -574,8 +594,11 @@
       <c r="J1" t="s">
         <v>7</v>
       </c>
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -603,8 +626,11 @@
       <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -635,8 +661,11 @@
       <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -664,8 +693,11 @@
       <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -693,6 +725,12 @@
       <c r="J5" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="J6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Editor/ExcelData/WeaponData.xlsx
+++ b/Assets/Editor/ExcelData/WeaponData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD724CF-C41F-4F72-A078-4DA3B92E024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA8B951-B548-4909-A7E2-334942418F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Range</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,26 +135,6 @@
   </si>
   <si>
     <t>Arrow</t>
-  </si>
-  <si>
-    <t>soundAddressable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sounds/Sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sounds/Bow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sounds/Shield</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sounds/Hammer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -547,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -563,7 +543,7 @@
     <col min="11" max="11" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -594,11 +574,8 @@
       <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -626,11 +603,8 @@
       <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -661,11 +635,8 @@
       <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -693,11 +664,8 @@
       <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -725,12 +693,6 @@
       <c r="J5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="J6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
